--- a/C题/附件/附件5/result1.xlsx
+++ b/C题/附件/附件5/result1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="计划购电量" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="充放电量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>

--- a/C题/附件/附件5/result1.xlsx
+++ b/C题/附件/附件5/result1.xlsx
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>574.0505000000001</v>
+        <v>1407.3838</v>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>575.7406</v>
+        <v>1409.0739</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>576.4712</v>
+        <v>1409.8045</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>577.828</v>
+        <v>911.1614</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="B138" s="7" t="n">
-        <v>1400.0808</v>
+        <v>566.7474</v>
       </c>
     </row>
     <row r="139" ht="14" customHeight="1">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="B140" s="7" t="n">
-        <v>1234.4968</v>
+        <v>567.8302</v>
       </c>
     </row>
     <row r="141" ht="14" customHeight="1">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="B141" s="7" t="n">
-        <v>1402.692</v>
+        <v>569.3586</v>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="B143" s="7" t="n">
-        <v>1404.9487</v>
+        <v>904.9487</v>
       </c>
     </row>
     <row r="144" ht="14" customHeight="1">
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1666.6667</v>
+        <v>4500</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8550</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="3" ht="14" customFormat="1" customHeight="1" s="5">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8550</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="4" ht="14" customFormat="1" customHeight="1" s="5">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8166.6667</v>
+        <v>5333.3333</v>
       </c>
       <c r="C7" t="n">
         <v>2859.8681</v>
